--- a/tutorials/data/hp_data_supervised.xlsx
+++ b/tutorials/data/hp_data_supervised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nova174\PycharmProjects\pandaprosumer_fork\tutorials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19004A-6D7C-4D6E-9561-ADE114C5E340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082BDFA5-4547-4BC1-A87C-9E46E369BB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,6 +465,7 @@
   <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="39.85546875" customWidth="1"/>
     <col min="4" max="4" width="31.7109375" customWidth="1"/>
     <col min="5" max="5" width="26.140625" customWidth="1"/>
   </cols>
@@ -491,7 +492,7 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C2">
         <v>80</v>
@@ -508,7 +509,7 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C3">
         <v>80</v>
@@ -525,7 +526,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C4">
         <v>80</v>
@@ -542,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C5">
         <v>80</v>
@@ -559,7 +560,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C6">
         <v>80</v>
@@ -576,7 +577,7 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C7">
         <v>80</v>
@@ -593,7 +594,7 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C8">
         <v>80</v>
@@ -610,7 +611,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C9">
         <v>80</v>
@@ -627,7 +628,7 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C10">
         <v>80</v>
@@ -644,7 +645,7 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C11">
         <v>80</v>
@@ -661,7 +662,7 @@
         <v>25</v>
       </c>
       <c r="B12">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -678,7 +679,7 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C13">
         <v>80</v>
@@ -695,7 +696,7 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C14">
         <v>80</v>
@@ -712,7 +713,7 @@
         <v>25</v>
       </c>
       <c r="B15">
-        <v>675</v>
+        <v>1000</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -729,7 +730,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>675</v>
+        <v>1000</v>
       </c>
       <c r="C16">
         <v>80</v>
@@ -746,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C17">
         <v>80</v>
@@ -763,7 +764,7 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -780,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="B19">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C19">
         <v>80</v>
@@ -797,7 +798,7 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="C20">
         <v>80</v>
@@ -814,7 +815,7 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C21">
         <v>80</v>
@@ -831,7 +832,7 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C22">
         <v>80</v>
@@ -848,7 +849,7 @@
         <v>25</v>
       </c>
       <c r="B23">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="C23">
         <v>80</v>
@@ -865,7 +866,7 @@
         <v>25</v>
       </c>
       <c r="B24">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C24">
         <v>80</v>
@@ -882,7 +883,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C25">
         <v>80</v>
@@ -899,7 +900,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C26">
         <v>80</v>
@@ -916,7 +917,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C27">
         <v>80</v>
@@ -925,7 +926,7 @@
         <v>20</v>
       </c>
       <c r="E27">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -933,7 +934,7 @@
         <v>25</v>
       </c>
       <c r="B28">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C28">
         <v>80</v>
@@ -942,7 +943,7 @@
         <v>20</v>
       </c>
       <c r="E28">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -950,7 +951,7 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C29">
         <v>80</v>
@@ -959,7 +960,7 @@
         <v>20</v>
       </c>
       <c r="E29">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -967,7 +968,7 @@
         <v>25</v>
       </c>
       <c r="B30">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C30">
         <v>80</v>
@@ -976,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="E30">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -984,7 +985,7 @@
         <v>25</v>
       </c>
       <c r="B31">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C31">
         <v>80</v>
@@ -993,7 +994,7 @@
         <v>20</v>
       </c>
       <c r="E31">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1001,7 +1002,7 @@
         <v>25</v>
       </c>
       <c r="B32">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C32">
         <v>80</v>
@@ -1010,7 +1011,7 @@
         <v>20</v>
       </c>
       <c r="E32">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1018,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="B33">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C33">
         <v>80</v>
@@ -1027,7 +1028,7 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1035,7 +1036,7 @@
         <v>25</v>
       </c>
       <c r="B34">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C34">
         <v>80</v>
@@ -1044,7 +1045,7 @@
         <v>20</v>
       </c>
       <c r="E34">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1052,7 +1053,7 @@
         <v>25</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C35">
         <v>80</v>
@@ -1061,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="E35">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1069,7 +1070,7 @@
         <v>25</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C36">
         <v>80</v>
@@ -1078,7 +1079,7 @@
         <v>20</v>
       </c>
       <c r="E36">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1086,7 +1087,7 @@
         <v>25</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C37">
         <v>80</v>
@@ -1095,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="E37">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1103,7 +1104,7 @@
         <v>25</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C38">
         <v>80</v>
@@ -1112,7 +1113,7 @@
         <v>20</v>
       </c>
       <c r="E38">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1120,7 +1121,7 @@
         <v>25</v>
       </c>
       <c r="B39">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C39">
         <v>80</v>
@@ -1129,7 +1130,7 @@
         <v>20</v>
       </c>
       <c r="E39">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1137,7 +1138,7 @@
         <v>25</v>
       </c>
       <c r="B40">
-        <v>321</v>
+        <v>1000</v>
       </c>
       <c r="C40">
         <v>80</v>
@@ -1146,7 +1147,7 @@
         <v>20</v>
       </c>
       <c r="E40">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1154,7 +1155,7 @@
         <v>25</v>
       </c>
       <c r="B41">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C41">
         <v>80</v>
@@ -1163,7 +1164,7 @@
         <v>20</v>
       </c>
       <c r="E41">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1171,7 +1172,7 @@
         <v>25</v>
       </c>
       <c r="B42">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C42">
         <v>80</v>
@@ -1180,7 +1181,7 @@
         <v>20</v>
       </c>
       <c r="E42">
-        <v>7.0000000000000007E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1188,7 +1189,7 @@
         <v>25</v>
       </c>
       <c r="B43">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C43">
         <v>80</v>
@@ -1197,7 +1198,7 @@
         <v>20</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1205,7 +1206,7 @@
         <v>25</v>
       </c>
       <c r="B44">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C44">
         <v>80</v>
@@ -1214,7 +1215,7 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1222,7 +1223,7 @@
         <v>25</v>
       </c>
       <c r="B45">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C45">
         <v>80</v>
@@ -1231,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1239,7 +1240,7 @@
         <v>25</v>
       </c>
       <c r="B46">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="C46">
         <v>80</v>
@@ -1248,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1256,7 +1257,7 @@
         <v>25</v>
       </c>
       <c r="B47">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C47">
         <v>80</v>
@@ -1265,7 +1266,7 @@
         <v>20</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1273,7 +1274,7 @@
         <v>25</v>
       </c>
       <c r="B48">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C48">
         <v>80</v>
@@ -1282,7 +1283,7 @@
         <v>20</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1290,7 +1291,7 @@
         <v>25</v>
       </c>
       <c r="B49">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C49">
         <v>80</v>
@@ -1299,7 +1300,7 @@
         <v>20</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1307,7 +1308,7 @@
         <v>25</v>
       </c>
       <c r="B50">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C50">
         <v>80</v>
@@ -1316,7 +1317,7 @@
         <v>20</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1324,7 +1325,7 @@
         <v>25</v>
       </c>
       <c r="B51">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C51">
         <v>80</v>
@@ -1333,7 +1334,7 @@
         <v>20</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1341,7 +1342,7 @@
         <v>25</v>
       </c>
       <c r="B52">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C52">
         <v>80</v>
@@ -1350,7 +1351,7 @@
         <v>20</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1358,7 +1359,7 @@
         <v>25</v>
       </c>
       <c r="B53">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C53">
         <v>80</v>
@@ -1367,7 +1368,7 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1375,7 +1376,7 @@
         <v>25</v>
       </c>
       <c r="B54">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C54">
         <v>80</v>
@@ -1384,7 +1385,7 @@
         <v>20</v>
       </c>
       <c r="E54">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1392,7 +1393,7 @@
         <v>25</v>
       </c>
       <c r="B55">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C55">
         <v>80</v>
@@ -1401,7 +1402,7 @@
         <v>20</v>
       </c>
       <c r="E55">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1409,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="B56">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C56">
         <v>80</v>
@@ -1418,7 +1419,7 @@
         <v>20</v>
       </c>
       <c r="E56">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1426,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="B57">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C57">
         <v>80</v>
@@ -1435,7 +1436,7 @@
         <v>20</v>
       </c>
       <c r="E57">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1443,7 +1444,7 @@
         <v>25</v>
       </c>
       <c r="B58">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C58">
         <v>80</v>
@@ -1452,7 +1453,7 @@
         <v>20</v>
       </c>
       <c r="E58">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1460,7 +1461,7 @@
         <v>25</v>
       </c>
       <c r="B59">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C59">
         <v>80</v>
@@ -1469,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="E59">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1477,7 +1478,7 @@
         <v>25</v>
       </c>
       <c r="B60">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C60">
         <v>80</v>
@@ -1486,7 +1487,7 @@
         <v>20</v>
       </c>
       <c r="E60">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1494,7 +1495,7 @@
         <v>25</v>
       </c>
       <c r="B61">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C61">
         <v>80</v>
@@ -1503,7 +1504,7 @@
         <v>20</v>
       </c>
       <c r="E61">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1511,7 +1512,7 @@
         <v>25</v>
       </c>
       <c r="B62">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C62">
         <v>80</v>
@@ -1520,7 +1521,7 @@
         <v>20</v>
       </c>
       <c r="E62">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1528,7 +1529,7 @@
         <v>25</v>
       </c>
       <c r="B63">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C63">
         <v>80</v>
@@ -1537,7 +1538,7 @@
         <v>20</v>
       </c>
       <c r="E63">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1545,7 +1546,7 @@
         <v>25</v>
       </c>
       <c r="B64">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C64">
         <v>80</v>
@@ -1554,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E64">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1562,7 +1563,7 @@
         <v>25</v>
       </c>
       <c r="B65">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C65">
         <v>80</v>
@@ -1571,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="E65">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1579,7 +1580,7 @@
         <v>25</v>
       </c>
       <c r="B66">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C66">
         <v>80</v>
@@ -1588,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="E66">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1596,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="B67">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C67">
         <v>80</v>
@@ -1605,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="E67">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1613,7 +1614,7 @@
         <v>25</v>
       </c>
       <c r="B68">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C68">
         <v>80</v>
@@ -1622,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="E68">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1630,7 +1631,7 @@
         <v>25</v>
       </c>
       <c r="B69">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C69">
         <v>80</v>
@@ -1639,7 +1640,7 @@
         <v>20</v>
       </c>
       <c r="E69">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -1647,7 +1648,7 @@
         <v>25</v>
       </c>
       <c r="B70">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C70">
         <v>80</v>
@@ -1656,7 +1657,7 @@
         <v>20</v>
       </c>
       <c r="E70">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1664,7 +1665,7 @@
         <v>25</v>
       </c>
       <c r="B71">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -1673,7 +1674,7 @@
         <v>20</v>
       </c>
       <c r="E71">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -1681,7 +1682,7 @@
         <v>25</v>
       </c>
       <c r="B72">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -1690,7 +1691,7 @@
         <v>20</v>
       </c>
       <c r="E72">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1698,7 +1699,7 @@
         <v>25</v>
       </c>
       <c r="B73">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C73">
         <v>80</v>
@@ -1707,7 +1708,7 @@
         <v>20</v>
       </c>
       <c r="E73">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1715,7 +1716,7 @@
         <v>25</v>
       </c>
       <c r="B74">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C74">
         <v>80</v>
@@ -1724,7 +1725,7 @@
         <v>20</v>
       </c>
       <c r="E74">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -1732,7 +1733,7 @@
         <v>25</v>
       </c>
       <c r="B75">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C75">
         <v>80</v>
@@ -1741,7 +1742,7 @@
         <v>20</v>
       </c>
       <c r="E75">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -1749,7 +1750,7 @@
         <v>25</v>
       </c>
       <c r="B76">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C76">
         <v>80</v>
@@ -1758,7 +1759,7 @@
         <v>20</v>
       </c>
       <c r="E76">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -1766,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="B77">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C77">
         <v>80</v>
@@ -1775,7 +1776,7 @@
         <v>20</v>
       </c>
       <c r="E77">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -1783,7 +1784,7 @@
         <v>25</v>
       </c>
       <c r="B78">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C78">
         <v>80</v>
@@ -1792,7 +1793,7 @@
         <v>20</v>
       </c>
       <c r="E78">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -1800,7 +1801,7 @@
         <v>25</v>
       </c>
       <c r="B79">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C79">
         <v>80</v>
@@ -1809,7 +1810,7 @@
         <v>20</v>
       </c>
       <c r="E79">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -1817,7 +1818,7 @@
         <v>25</v>
       </c>
       <c r="B80">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C80">
         <v>80</v>
@@ -1826,7 +1827,7 @@
         <v>20</v>
       </c>
       <c r="E80">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -1834,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="B81">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1843,7 +1844,7 @@
         <v>20</v>
       </c>
       <c r="E81">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -1851,7 +1852,7 @@
         <v>25</v>
       </c>
       <c r="B82">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C82">
         <v>80</v>
@@ -1860,7 +1861,7 @@
         <v>20</v>
       </c>
       <c r="E82">
-        <v>0.01</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -1868,7 +1869,7 @@
         <v>25</v>
       </c>
       <c r="B83">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C83">
         <v>80</v>
@@ -1877,7 +1878,7 @@
         <v>20</v>
       </c>
       <c r="E83">
-        <v>0.01</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -1885,7 +1886,7 @@
         <v>25</v>
       </c>
       <c r="B84">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C84">
         <v>80</v>
@@ -1894,7 +1895,7 @@
         <v>20</v>
       </c>
       <c r="E84">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,7 +1903,7 @@
         <v>25</v>
       </c>
       <c r="B85">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C85">
         <v>80</v>
@@ -1911,7 +1912,7 @@
         <v>20</v>
       </c>
       <c r="E85">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -1919,7 +1920,7 @@
         <v>25</v>
       </c>
       <c r="B86">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C86">
         <v>80</v>
@@ -1928,7 +1929,7 @@
         <v>20</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1937,7 @@
         <v>25</v>
       </c>
       <c r="B87">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C87">
         <v>80</v>
@@ -1945,7 +1946,7 @@
         <v>20</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,7 +1954,7 @@
         <v>25</v>
       </c>
       <c r="B88">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C88">
         <v>80</v>
@@ -1962,7 +1963,7 @@
         <v>20</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -1970,7 +1971,7 @@
         <v>25</v>
       </c>
       <c r="B89">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C89">
         <v>80</v>
@@ -1979,7 +1980,7 @@
         <v>20</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -1987,7 +1988,7 @@
         <v>25</v>
       </c>
       <c r="B90">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C90">
         <v>80</v>
@@ -1996,7 +1997,7 @@
         <v>20</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2004,7 +2005,7 @@
         <v>25</v>
       </c>
       <c r="B91">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C91">
         <v>80</v>
@@ -2013,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="E91">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2021,7 +2022,7 @@
         <v>25</v>
       </c>
       <c r="B92">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C92">
         <v>80</v>
@@ -2030,7 +2031,7 @@
         <v>20</v>
       </c>
       <c r="E92">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2038,7 +2039,7 @@
         <v>25</v>
       </c>
       <c r="B93">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C93">
         <v>80</v>
@@ -2047,7 +2048,7 @@
         <v>20</v>
       </c>
       <c r="E93">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2055,7 +2056,7 @@
         <v>25</v>
       </c>
       <c r="B94">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C94">
         <v>80</v>
@@ -2064,7 +2065,7 @@
         <v>20</v>
       </c>
       <c r="E94">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2072,7 +2073,7 @@
         <v>25</v>
       </c>
       <c r="B95">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C95">
         <v>80</v>
@@ -2081,7 +2082,7 @@
         <v>20</v>
       </c>
       <c r="E95">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2089,7 +2090,7 @@
         <v>25</v>
       </c>
       <c r="B96">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C96">
         <v>80</v>
@@ -2098,7 +2099,7 @@
         <v>20</v>
       </c>
       <c r="E96">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2106,7 +2107,7 @@
         <v>25</v>
       </c>
       <c r="B97">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C97">
         <v>80</v>
@@ -2115,7 +2116,7 @@
         <v>20</v>
       </c>
       <c r="E97">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
